--- a/output/pdf_financials_xlsx/WISE.xlsx
+++ b/output/pdf_financials_xlsx/WISE.xlsx
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.038138</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.042029</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.038138</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.042029</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.148371</v>
+        <v>0.110233</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.06300699999999999</v>
+        <v>0.020978</v>
       </c>
     </row>
     <row r="49">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/WISE.xlsx
+++ b/output/pdf_financials_xlsx/WISE.xlsx
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-0.019864</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.054493</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -2942,7 +2942,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>-0.019864</v>
       </c>
@@ -2968,7 +2972,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>0.054493</v>
       </c>
@@ -3050,7 +3058,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>3.511875</v>
       </c>
